--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run8/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.4034,0.0898,0.0236,0.5771</t>
-  </si>
-  <si>
-    <t>0.0032,0.0010,0.0005,0.9983</t>
-  </si>
-  <si>
-    <t>0.5237,0.0045,0.0041,0.6199</t>
-  </si>
-  <si>
-    <t>0.0719,0.0109,0.0012,0.9709</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9961,0.0015,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9890,0.0094,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9900,0.0054,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.9964,0.0012,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9892,0.0083,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.9973,0.0006,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9970,0.0012,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.7673,0.0445,0.0930,0.0309</t>
-  </si>
-  <si>
-    <t>0.4488,0.0693,0.5799,0.0104</t>
-  </si>
-  <si>
-    <t>0.4069,0.0622,0.6744,0.0055</t>
-  </si>
-  <si>
-    <t>0.1763,0.0480,0.8228,0.0016</t>
-  </si>
-  <si>
-    <t>0.7560,0.1082,0.1089,0.0227</t>
-  </si>
-  <si>
-    <t>0.0045,0.9926,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.0125,0.9855,0.0066,0.0001</t>
-  </si>
-  <si>
-    <t>0.1929,0.8807,0.0038,0.0009</t>
-  </si>
-  <si>
-    <t>0.0336,0.9544,0.0047,0.0034</t>
-  </si>
-  <si>
-    <t>0.0013,0.9956,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.1201,0.0087,0.8322,0.0929</t>
-  </si>
-  <si>
-    <t>0.5334,0.0219,0.2322,0.1641</t>
-  </si>
-  <si>
-    <t>0.0230,0.0174,0.9481,0.0533</t>
-  </si>
-  <si>
-    <t>0.1751,0.0171,0.8493,0.0336</t>
-  </si>
-  <si>
-    <t>0.1737,0.0117,0.9036,0.0121</t>
-  </si>
-  <si>
-    <t>0.0666,0.0184,0.9147,0.0397</t>
-  </si>
-  <si>
-    <t>0.0269,0.0027,0.9776,0.0072</t>
-  </si>
-  <si>
-    <t>0.3624,0.7584,0.0045,0.0012</t>
-  </si>
-  <si>
-    <t>0.6827,0.0486,0.2909,0.0460</t>
-  </si>
-  <si>
-    <t>0.0057,0.0091,0.9838,0.0158</t>
-  </si>
-  <si>
-    <t>0.0127,0.6863,0.6854,0.0001</t>
-  </si>
-  <si>
-    <t>0.9396,0.0259,0.0042,0.0114</t>
-  </si>
-  <si>
-    <t>0.6836,0.1085,0.2223,0.0152</t>
-  </si>
-  <si>
-    <t>0.8682,0.2249,0.0065,0.0010</t>
-  </si>
-  <si>
-    <t>0.0378,0.9035,0.3539,0.0015</t>
-  </si>
-  <si>
-    <t>0.0096,0.7420,0.8641,0.0024</t>
-  </si>
-  <si>
-    <t>0.0129,0.0193,0.8364,0.2043</t>
-  </si>
-  <si>
-    <t>0.1162,0.2342,0.7338,0.0522</t>
-  </si>
-  <si>
-    <t>0.1947,0.0051,0.6234,0.1540</t>
-  </si>
-  <si>
-    <t>0.0261,0.0862,0.9216,0.0105</t>
-  </si>
-  <si>
-    <t>0.0096,0.9441,0.1031,0.0023</t>
-  </si>
-  <si>
-    <t>0.0284,0.3429,0.7822,0.0708</t>
-  </si>
-  <si>
-    <t>0.0836,0.5767,0.0043,0.6339</t>
-  </si>
-  <si>
-    <t>0.0007,0.9858,0.0017,0.0750</t>
-  </si>
-  <si>
-    <t>0.0017,0.9887,0.0190,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.9984,0.0177,0.0002</t>
-  </si>
-  <si>
-    <t>0.0037,0.0110,0.9401,0.0790</t>
-  </si>
-  <si>
-    <t>0.0058,0.3013,0.9563,0.0005</t>
-  </si>
-  <si>
-    <t>0.0690,0.1071,0.8659,0.0100</t>
-  </si>
-  <si>
-    <t>0.0470,0.0132,0.9576,0.0056</t>
-  </si>
-  <si>
-    <t>0.0029,0.0075,0.9877,0.0166</t>
-  </si>
-  <si>
-    <t>0.0145,0.0191,0.9670,0.0023</t>
-  </si>
-  <si>
-    <t>0.9788,0.0393,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9949,0.0060,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9580,0.0232,0.0019,0.0102</t>
-  </si>
-  <si>
-    <t>0.1323,0.1755,0.8072,0.0080</t>
-  </si>
-  <si>
-    <t>0.9929,0.0070,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9928,0.0047,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9788,0.0312,0.0021,0.0003</t>
-  </si>
-  <si>
-    <t>0.0025,0.6659,0.9715,0.0008</t>
-  </si>
-  <si>
-    <t>0.0204,0.0664,0.9599,0.0038</t>
-  </si>
-  <si>
-    <t>0.0333,0.0550,0.8977,0.0394</t>
-  </si>
-  <si>
-    <t>0.0024,0.8047,0.8878,0.0003</t>
-  </si>
-  <si>
-    <t>0.0053,0.0773,0.9723,0.0043</t>
-  </si>
-  <si>
-    <t>0.1234,0.8609,0.0187,0.0003</t>
-  </si>
-  <si>
-    <t>0.0026,0.9919,0.0081,0.0009</t>
-  </si>
-  <si>
-    <t>0.8991,0.0276,0.1156,0.0028</t>
-  </si>
-  <si>
-    <t>0.4868,0.4482,0.1352,0.0017</t>
-  </si>
-  <si>
-    <t>0.0079,0.0322,0.9771,0.0179</t>
-  </si>
-  <si>
-    <t>0.0032,0.7910,0.9016,0.0010</t>
-  </si>
-  <si>
-    <t>0.0043,0.9123,0.6765,0.0009</t>
-  </si>
-  <si>
-    <t>0.0025,0.9841,0.1718,0.0018</t>
-  </si>
-  <si>
-    <t>0.0042,0.8619,0.8360,0.0010</t>
-  </si>
-  <si>
-    <t>0.0059,0.0020,0.1232,0.9671</t>
-  </si>
-  <si>
-    <t>0.0035,0.0020,0.0002,0.9981</t>
-  </si>
-  <si>
-    <t>0.0085,0.0056,0.0001,0.9958</t>
-  </si>
-  <si>
-    <t>0.0187,0.0029,0.0015,0.9920</t>
-  </si>
-  <si>
-    <t>0.0056,0.0253,0.0032,0.9934</t>
-  </si>
-  <si>
-    <t>0.0026,0.0078,0.0003,0.9978</t>
-  </si>
-  <si>
-    <t>0.0014,0.7670,0.9515,0.0002</t>
-  </si>
-  <si>
-    <t>0.0056,0.3942,0.9582,0.0022</t>
-  </si>
-  <si>
-    <t>0.0181,0.2238,0.8529,0.0004</t>
-  </si>
-  <si>
-    <t>0.0067,0.6412,0.8783,0.0010</t>
-  </si>
-  <si>
-    <t>0.0017,0.9655,0.6235,0.0003</t>
-  </si>
-  <si>
-    <t>0.0035,0.8250,0.7195,0.0002</t>
-  </si>
-  <si>
-    <t>0.9964,0.0038,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9939,0.0034,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9917,0.0046,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9948,0.0024,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9807,0.0190,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9938,0.0033,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9931,0.0048,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9926,0.0040,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9978,0.0008,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9936,0.0032,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9953,0.0022,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9961,0.0011,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9974,0.0005,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9911,0.0085,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.0020,0.0016,0.9944,0.0087</t>
-  </si>
-  <si>
-    <t>0.1558,0.0827,0.7578,0.0093</t>
-  </si>
-  <si>
-    <t>0.5353,0.0157,0.1440,0.2507</t>
-  </si>
-  <si>
-    <t>0.0450,0.0099,0.9563,0.0152</t>
-  </si>
-  <si>
-    <t>0.0128,0.9787,0.0010,0.0016</t>
-  </si>
-  <si>
-    <t>0.0443,0.9621,0.0030,0.0007</t>
-  </si>
-  <si>
-    <t>0.0148,0.9740,0.0003,0.0037</t>
-  </si>
-  <si>
-    <t>0.3704,0.7873,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.0067,0.9846,0.0018,0.0013</t>
-  </si>
-  <si>
-    <t>0.0022,0.9934,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.3314,0.7872,0.0042,0.0005</t>
-  </si>
-  <si>
-    <t>0.8009,0.0381,0.1093,0.0158</t>
-  </si>
-  <si>
-    <t>0.1805,0.0095,0.9134,0.0081</t>
-  </si>
-  <si>
-    <t>0.4731,0.0996,0.4915,0.0116</t>
-  </si>
-  <si>
-    <t>0.5788,0.1762,0.2751,0.0285</t>
-  </si>
-  <si>
-    <t>0.2803,0.1097,0.0634,0.6861</t>
-  </si>
-  <si>
-    <t>0.0002,0.9982,0.0035,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.9928,0.0061,0.0093</t>
-  </si>
-  <si>
-    <t>0.0023,0.9783,0.0027,0.0577</t>
-  </si>
-  <si>
-    <t>0.0002,0.9857,0.6552,0.0002</t>
-  </si>
-  <si>
-    <t>0.0158,0.9752,0.0403,0.0009</t>
-  </si>
-  <si>
-    <t>0.6673,0.3748,0.0559,0.0036</t>
-  </si>
-  <si>
-    <t>0.5987,0.5859,0.0083,0.0007</t>
-  </si>
-  <si>
-    <t>0.9933,0.0019,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9896,0.0023,0.0011,0.0032</t>
-  </si>
-  <si>
-    <t>0.9836,0.0016,0.0005,0.0123</t>
-  </si>
-  <si>
-    <t>0.9838,0.0081,0.0018,0.0022</t>
-  </si>
-  <si>
-    <t>0.9967,0.0003,0.0000,0.0017</t>
-  </si>
-  <si>
-    <t>0.9846,0.0118,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.9959,0.0008,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9750,0.0156,0.0091,0.0011</t>
-  </si>
-  <si>
-    <t>0.0031,0.4204,0.9640,0.0009</t>
-  </si>
-  <si>
-    <t>0.0154,0.5865,0.8359,0.0017</t>
-  </si>
-  <si>
-    <t>0.0041,0.7494,0.7156,0.0005</t>
-  </si>
-  <si>
-    <t>0.0072,0.0404,0.9779,0.0011</t>
-  </si>
-  <si>
-    <t>0.7555,0.0412,0.1028,0.0483</t>
-  </si>
-  <si>
-    <t>0.8246,0.0962,0.0381,0.0195</t>
-  </si>
-  <si>
-    <t>0.1226,0.0012,0.9538,0.0117</t>
-  </si>
-  <si>
-    <t>0.3420,0.3025,0.3773,0.0279</t>
-  </si>
-  <si>
-    <t>0.0222,0.0007,0.0011,0.9917</t>
-  </si>
-  <si>
-    <t>0.0005,0.0005,0.0007,0.9992</t>
-  </si>
-  <si>
-    <t>0.0090,0.0014,0.0034,0.9939</t>
-  </si>
-  <si>
-    <t>0.0080,0.0006,0.0011,0.9959</t>
-  </si>
-  <si>
-    <t>0.0029,0.9419,0.6879,0.0008</t>
-  </si>
-  <si>
-    <t>0.9896,0.0014,0.0002,0.0040</t>
-  </si>
-  <si>
-    <t>0.8639,0.2352,0.0016,0.0017</t>
-  </si>
-  <si>
-    <t>0.9844,0.0013,0.0000,0.0079</t>
-  </si>
-  <si>
-    <t>0.3766,0.7200,0.0192,0.0010</t>
-  </si>
-  <si>
-    <t>0.9834,0.0009,0.0006,0.0135</t>
-  </si>
-  <si>
-    <t>0.7435,0.0157,0.0321,0.2134</t>
-  </si>
-  <si>
-    <t>0.9761,0.0060,0.0020,0.0075</t>
-  </si>
-  <si>
-    <t>0.0001,0.0290,0.9911,0.0086</t>
-  </si>
-  <si>
-    <t>0.9350,0.0032,0.0136,0.0242</t>
-  </si>
-  <si>
-    <t>0.9655,0.0028,0.0016,0.0245</t>
-  </si>
-  <si>
-    <t>0.7571,0.2275,0.0483,0.0109</t>
-  </si>
-  <si>
-    <t>0.9170,0.0318,0.0187,0.0076</t>
-  </si>
-  <si>
-    <t>0.9409,0.0894,0.0061,0.0007</t>
-  </si>
-  <si>
-    <t>0.2328,0.7648,0.0201,0.0218</t>
-  </si>
-  <si>
-    <t>0.9180,0.1081,0.0057,0.0015</t>
-  </si>
-  <si>
-    <t>0.9082,0.0463,0.0209,0.0044</t>
-  </si>
-  <si>
-    <t>0.9646,0.0246,0.0003,0.0029</t>
-  </si>
-  <si>
-    <t>0.9882,0.0017,0.0000,0.0033</t>
-  </si>
-  <si>
-    <t>0.9717,0.0197,0.0022,0.0029</t>
-  </si>
-  <si>
-    <t>0.9835,0.0006,0.0003,0.0139</t>
-  </si>
-  <si>
-    <t>0.9818,0.0075,0.0008,0.0042</t>
-  </si>
-  <si>
-    <t>0.9867,0.0015,0.0002,0.0079</t>
-  </si>
-  <si>
-    <t>0.9937,0.0007,0.0001,0.0029</t>
-  </si>
-  <si>
-    <t>0.9909,0.0013,0.0002,0.0038</t>
-  </si>
-  <si>
-    <t>0.8933,0.1831,0.0024,0.0019</t>
-  </si>
-  <si>
-    <t>0.6669,0.4684,0.0155,0.0017</t>
-  </si>
-  <si>
-    <t>0.2166,0.8682,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.7125,0.2899,0.0609,0.0200</t>
-  </si>
-  <si>
-    <t>0.9771,0.0238,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9396,0.0503,0.0135,0.0027</t>
-  </si>
-  <si>
-    <t>0.9870,0.0130,0.0021,0.0003</t>
-  </si>
-  <si>
-    <t>0.9271,0.0902,0.0011,0.0030</t>
-  </si>
-  <si>
-    <t>0.0394,0.0993,0.9429,0.0010</t>
-  </si>
-  <si>
-    <t>0.9756,0.0306,0.0029,0.0005</t>
-  </si>
-  <si>
-    <t>0.0224,0.0250,0.9739,0.0017</t>
-  </si>
-  <si>
-    <t>0.0099,0.0519,0.9810,0.0016</t>
-  </si>
-  <si>
-    <t>0.0292,0.0097,0.9668,0.0056</t>
-  </si>
-  <si>
-    <t>0.0023,0.1918,0.9824,0.0013</t>
-  </si>
-  <si>
-    <t>0.0342,0.0223,0.9178,0.0756</t>
-  </si>
-  <si>
-    <t>0.0078,0.0027,0.9914,0.0018</t>
-  </si>
-  <si>
-    <t>0.0189,0.0081,0.9549,0.0691</t>
-  </si>
-  <si>
-    <t>0.3052,0.0310,0.6924,0.0530</t>
-  </si>
-  <si>
-    <t>0.3096,0.0236,0.8107,0.0068</t>
-  </si>
-  <si>
-    <t>0.7247,0.0258,0.2706,0.0170</t>
-  </si>
-  <si>
-    <t>0.7365,0.0461,0.2651,0.0050</t>
-  </si>
-  <si>
-    <t>0.2407,0.6665,0.1071,0.0038</t>
-  </si>
-  <si>
-    <t>0.5901,0.1648,0.2643,0.0385</t>
-  </si>
-  <si>
-    <t>0.3870,0.1869,0.5235,0.0664</t>
-  </si>
-  <si>
-    <t>0.5169,0.1579,0.4116,0.0252</t>
-  </si>
-  <si>
-    <t>0.7032,0.4541,0.0091,0.0015</t>
-  </si>
-  <si>
-    <t>0.7233,0.5116,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.9409,0.1144,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9873,0.0083,0.0019,0.0008</t>
-  </si>
-  <si>
-    <t>0.9698,0.0535,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.7043,0.0697,0.2447,0.0081</t>
-  </si>
-  <si>
-    <t>0.8119,0.0376,0.1669,0.0040</t>
-  </si>
-  <si>
-    <t>0.2245,0.0075,0.0679,0.7807</t>
-  </si>
-  <si>
-    <t>0.6287,0.0466,0.2742,0.0560</t>
-  </si>
-  <si>
-    <t>0.7139,0.0147,0.1694,0.0629</t>
-  </si>
-  <si>
-    <t>0.2253,0.0690,0.7427,0.0455</t>
-  </si>
-  <si>
-    <t>0.1323,0.3023,0.5601,0.0126</t>
-  </si>
-  <si>
-    <t>0.1133,0.1278,0.8016,0.0282</t>
-  </si>
-  <si>
-    <t>0.0524,0.0930,0.8875,0.0225</t>
-  </si>
-  <si>
-    <t>0.0203,0.0554,0.9445,0.0086</t>
-  </si>
-  <si>
-    <t>0.9869,0.0024,0.0001,0.0042</t>
-  </si>
-  <si>
-    <t>0.9920,0.0057,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9929,0.0026,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9902,0.0113,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9944,0.0033,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9948,0.0006,0.0000,0.0019</t>
-  </si>
-  <si>
-    <t>0.9974,0.0010,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9879,0.0134,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.0398,0.0390,0.9521,0.0093</t>
-  </si>
-  <si>
-    <t>0.7722,0.0345,0.2429,0.0157</t>
-  </si>
-  <si>
-    <t>0.7535,0.0393,0.0584,0.1343</t>
-  </si>
-  <si>
-    <t>0.0120,0.0537,0.9652,0.0019</t>
-  </si>
-  <si>
-    <t>0.0037,0.0722,0.9854,0.0024</t>
-  </si>
-  <si>
-    <t>0.0518,0.0685,0.8819,0.0079</t>
-  </si>
-  <si>
-    <t>0.0073,0.0063,0.9849,0.0055</t>
-  </si>
-  <si>
-    <t>0.0638,0.0258,0.9113,0.0158</t>
-  </si>
-  <si>
-    <t>0.0007,0.0036,0.9935,0.0069</t>
-  </si>
-  <si>
-    <t>0.0937,0.1304,0.7726,0.0058</t>
-  </si>
-  <si>
-    <t>0.0312,0.0240,0.9471,0.0109</t>
-  </si>
-  <si>
-    <t>0.7011,0.0187,0.2512,0.0283</t>
-  </si>
-  <si>
-    <t>0.3691,0.0151,0.7409,0.0219</t>
-  </si>
-  <si>
-    <t>0.6265,0.0431,0.0196,0.2390</t>
-  </si>
-  <si>
-    <t>0.9899,0.0080,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9961,0.0010,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9959,0.0046,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0031,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9947,0.0026,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9883,0.0120,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9959,0.0032,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9971,0.0012,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.0351,0.0286,0.9464,0.0010</t>
-  </si>
-  <si>
-    <t>0.0209,0.2528,0.9204,0.0033</t>
-  </si>
-  <si>
-    <t>0.0098,0.0177,0.9578,0.0279</t>
-  </si>
-  <si>
-    <t>0.2005,0.0161,0.8613,0.0051</t>
-  </si>
-  <si>
-    <t>0.0040,0.0365,0.9637,0.0221</t>
-  </si>
-  <si>
-    <t>0.1855,0.0314,0.0843,0.8018</t>
-  </si>
-  <si>
-    <t>0.0777,0.0205,0.8335,0.1569</t>
-  </si>
-  <si>
-    <t>0.2153,0.1260,0.4033,0.3121</t>
-  </si>
-  <si>
-    <t>0.4934,0.0012,0.0058,0.7003</t>
-  </si>
-  <si>
-    <t>0.0594,0.0215,0.0033,0.9690</t>
-  </si>
-  <si>
-    <t>0.0325,0.0008,0.0004,0.9919</t>
-  </si>
-  <si>
-    <t>0.0226,0.0004,0.0003,0.9948</t>
-  </si>
-  <si>
-    <t>0.0031,0.0010,0.0002,0.9984</t>
-  </si>
-  <si>
-    <t>0.7751,0.0178,0.0049,0.1960</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.8889,0.0260,0.0054,0.0621</t>
+  </si>
+  <si>
+    <t>0.0371,0.0079,0.0015,0.9849</t>
+  </si>
+  <si>
+    <t>0.2102,0.0086,0.0008,0.8979</t>
+  </si>
+  <si>
+    <t>0.1926,0.0112,0.0015,0.9178</t>
+  </si>
+  <si>
+    <t>0.9957,0.0022,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9888,0.0036,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.9901,0.0044,0.0020,0.0009</t>
+  </si>
+  <si>
+    <t>0.9964,0.0012,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9965,0.0038,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9958,0.0007,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9981,0.0006,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9947,0.0015,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.7808,0.1862,0.0452,0.0078</t>
+  </si>
+  <si>
+    <t>0.1698,0.2212,0.6639,0.0021</t>
+  </si>
+  <si>
+    <t>0.1388,0.0484,0.8445,0.0054</t>
+  </si>
+  <si>
+    <t>0.4248,0.1223,0.4957,0.0616</t>
+  </si>
+  <si>
+    <t>0.7644,0.0816,0.1541,0.0149</t>
+  </si>
+  <si>
+    <t>0.0069,0.9842,0.0253,0.0005</t>
+  </si>
+  <si>
+    <t>0.0152,0.9768,0.0029,0.0010</t>
+  </si>
+  <si>
+    <t>0.2154,0.8833,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.0527,0.9404,0.0064,0.0018</t>
+  </si>
+  <si>
+    <t>0.0014,0.9941,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.5653,0.0127,0.4513,0.0297</t>
+  </si>
+  <si>
+    <t>0.4557,0.0297,0.5041,0.0730</t>
+  </si>
+  <si>
+    <t>0.0207,0.0351,0.9365,0.0528</t>
+  </si>
+  <si>
+    <t>0.2399,0.0102,0.8709,0.0028</t>
+  </si>
+  <si>
+    <t>0.2646,0.0160,0.8555,0.0040</t>
+  </si>
+  <si>
+    <t>0.0177,0.0079,0.9735,0.0138</t>
+  </si>
+  <si>
+    <t>0.0023,0.0008,0.9888,0.0274</t>
+  </si>
+  <si>
+    <t>0.4366,0.6977,0.0107,0.0015</t>
+  </si>
+  <si>
+    <t>0.7822,0.1249,0.0982,0.0242</t>
+  </si>
+  <si>
+    <t>0.0139,0.0305,0.9690,0.0127</t>
+  </si>
+  <si>
+    <t>0.0287,0.9246,0.0758,0.0009</t>
+  </si>
+  <si>
+    <t>0.7796,0.1133,0.0035,0.0686</t>
+  </si>
+  <si>
+    <t>0.8095,0.1376,0.0511,0.0120</t>
+  </si>
+  <si>
+    <t>0.8486,0.1910,0.0261,0.0011</t>
+  </si>
+  <si>
+    <t>0.0093,0.9750,0.1450,0.0005</t>
+  </si>
+  <si>
+    <t>0.0102,0.8343,0.3989,0.0271</t>
+  </si>
+  <si>
+    <t>0.0168,0.0190,0.5490,0.5871</t>
+  </si>
+  <si>
+    <t>0.0745,0.2861,0.7451,0.0138</t>
+  </si>
+  <si>
+    <t>0.3593,0.0465,0.6468,0.0297</t>
+  </si>
+  <si>
+    <t>0.0551,0.0673,0.8997,0.0102</t>
+  </si>
+  <si>
+    <t>0.0061,0.9766,0.0104,0.0016</t>
+  </si>
+  <si>
+    <t>0.0145,0.3537,0.9122,0.0107</t>
+  </si>
+  <si>
+    <t>0.0325,0.8452,0.0096,0.3555</t>
+  </si>
+  <si>
+    <t>0.0006,0.9822,0.0088,0.0875</t>
+  </si>
+  <si>
+    <t>0.0007,0.9938,0.0337,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9973,0.0092,0.0039</t>
+  </si>
+  <si>
+    <t>0.0004,0.0336,0.9691,0.0190</t>
+  </si>
+  <si>
+    <t>0.0219,0.1214,0.9405,0.0021</t>
+  </si>
+  <si>
+    <t>0.2316,0.0431,0.7645,0.0122</t>
+  </si>
+  <si>
+    <t>0.0149,0.0008,0.9874,0.0095</t>
+  </si>
+  <si>
+    <t>0.0022,0.0035,0.9896,0.0239</t>
+  </si>
+  <si>
+    <t>0.0082,0.0051,0.9885,0.0012</t>
+  </si>
+  <si>
+    <t>0.9913,0.0049,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9865,0.0057,0.0010,0.0029</t>
+  </si>
+  <si>
+    <t>0.9875,0.0041,0.0006,0.0037</t>
+  </si>
+  <si>
+    <t>0.0094,0.2667,0.9650,0.0035</t>
+  </si>
+  <si>
+    <t>0.9920,0.0030,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.9925,0.0059,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9276,0.1113,0.0055,0.0016</t>
+  </si>
+  <si>
+    <t>0.0015,0.8396,0.9386,0.0002</t>
+  </si>
+  <si>
+    <t>0.0024,0.1446,0.9833,0.0025</t>
+  </si>
+  <si>
+    <t>0.0138,0.1133,0.9590,0.0041</t>
+  </si>
+  <si>
+    <t>0.0005,0.8873,0.9680,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0026,0.9947,0.0018</t>
+  </si>
+  <si>
+    <t>0.1769,0.6385,0.1052,0.0007</t>
+  </si>
+  <si>
+    <t>0.0036,0.9915,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9451,0.0266,0.0182,0.0026</t>
+  </si>
+  <si>
+    <t>0.8436,0.1792,0.0193,0.0048</t>
+  </si>
+  <si>
+    <t>0.2047,0.0818,0.7796,0.0231</t>
+  </si>
+  <si>
+    <t>0.0094,0.5948,0.8638,0.0007</t>
+  </si>
+  <si>
+    <t>0.0033,0.8836,0.8325,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.9639,0.6845,0.0013</t>
+  </si>
+  <si>
+    <t>0.0038,0.9325,0.6946,0.0006</t>
+  </si>
+  <si>
+    <t>0.0047,0.0040,0.0022,0.9955</t>
+  </si>
+  <si>
+    <t>0.0039,0.0098,0.0002,0.9970</t>
+  </si>
+  <si>
+    <t>0.0228,0.0010,0.0007,0.9921</t>
+  </si>
+  <si>
+    <t>0.0082,0.0151,0.0014,0.9934</t>
+  </si>
+  <si>
+    <t>0.0158,0.0059,0.0119,0.9845</t>
+  </si>
+  <si>
+    <t>0.0117,0.0024,0.0037,0.9917</t>
+  </si>
+  <si>
+    <t>0.0096,0.6727,0.8825,0.0028</t>
+  </si>
+  <si>
+    <t>0.0002,0.3399,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.0321,0.6858,0.5617,0.0037</t>
+  </si>
+  <si>
+    <t>0.0161,0.1594,0.9432,0.0015</t>
+  </si>
+  <si>
+    <t>0.0032,0.8934,0.4934,0.0001</t>
+  </si>
+  <si>
+    <t>0.0039,0.9421,0.4065,0.0007</t>
+  </si>
+  <si>
+    <t>0.9910,0.0031,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9973,0.0015,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9732,0.0266,0.0025,0.0016</t>
+  </si>
+  <si>
+    <t>0.9972,0.0005,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9944,0.0049,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9935,0.0039,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9922,0.0055,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9950,0.0017,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9952,0.0022,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9964,0.0015,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9950,0.0008,0.0000,0.0015</t>
+  </si>
+  <si>
+    <t>0.9971,0.0014,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9963,0.0033,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0017,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.0014,0.0034,0.9883,0.0320</t>
+  </si>
+  <si>
+    <t>0.0202,0.0226,0.9560,0.0295</t>
+  </si>
+  <si>
+    <t>0.6013,0.0563,0.2508,0.0735</t>
+  </si>
+  <si>
+    <t>0.1124,0.0107,0.9093,0.0146</t>
+  </si>
+  <si>
+    <t>0.0593,0.9386,0.0021,0.0035</t>
+  </si>
+  <si>
+    <t>0.0048,0.9892,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.0622,0.9442,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.6018,0.5746,0.0053,0.0025</t>
+  </si>
+  <si>
+    <t>0.0062,0.9858,0.0025,0.0011</t>
+  </si>
+  <si>
+    <t>0.0156,0.9754,0.0037,0.0005</t>
+  </si>
+  <si>
+    <t>0.6815,0.4298,0.0018,0.0027</t>
+  </si>
+  <si>
+    <t>0.5820,0.2572,0.1740,0.0431</t>
+  </si>
+  <si>
+    <t>0.2612,0.0224,0.7920,0.0318</t>
+  </si>
+  <si>
+    <t>0.6399,0.0660,0.2378,0.0738</t>
+  </si>
+  <si>
+    <t>0.3826,0.0904,0.5551,0.0322</t>
+  </si>
+  <si>
+    <t>0.1449,0.0347,0.0291,0.9011</t>
+  </si>
+  <si>
+    <t>0.0001,0.9977,0.0069,0.0015</t>
+  </si>
+  <si>
+    <t>0.0004,0.9928,0.0149,0.0107</t>
+  </si>
+  <si>
+    <t>0.1961,0.6853,0.0549,0.0932</t>
+  </si>
+  <si>
+    <t>0.0001,0.9534,0.9521,0.0000</t>
+  </si>
+  <si>
+    <t>0.0265,0.9631,0.0391,0.0005</t>
+  </si>
+  <si>
+    <t>0.7022,0.3645,0.0241,0.0046</t>
+  </si>
+  <si>
+    <t>0.7116,0.4755,0.0060,0.0016</t>
+  </si>
+  <si>
+    <t>0.9938,0.0020,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9876,0.0030,0.0012,0.0031</t>
+  </si>
+  <si>
+    <t>0.9836,0.0052,0.0020,0.0043</t>
+  </si>
+  <si>
+    <t>0.9842,0.0091,0.0038,0.0014</t>
+  </si>
+  <si>
+    <t>0.9967,0.0005,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9879,0.0067,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9925,0.0005,0.0001,0.0046</t>
+  </si>
+  <si>
+    <t>0.9598,0.0066,0.0060,0.0218</t>
+  </si>
+  <si>
+    <t>0.0055,0.6254,0.9087,0.0006</t>
+  </si>
+  <si>
+    <t>0.0148,0.8772,0.2377,0.0002</t>
+  </si>
+  <si>
+    <t>0.0248,0.1042,0.9170,0.0206</t>
+  </si>
+  <si>
+    <t>0.0451,0.2414,0.8475,0.0057</t>
+  </si>
+  <si>
+    <t>0.5765,0.1864,0.0715,0.1664</t>
+  </si>
+  <si>
+    <t>0.7281,0.0660,0.2390,0.0170</t>
+  </si>
+  <si>
+    <t>0.2805,0.0055,0.7864,0.0357</t>
+  </si>
+  <si>
+    <t>0.6569,0.0321,0.3308,0.0189</t>
+  </si>
+  <si>
+    <t>0.0513,0.0021,0.0010,0.9829</t>
+  </si>
+  <si>
+    <t>0.0009,0.0016,0.0016,0.9982</t>
+  </si>
+  <si>
+    <t>0.0027,0.0170,0.0003,0.9970</t>
+  </si>
+  <si>
+    <t>0.0301,0.0026,0.0024,0.9887</t>
+  </si>
+  <si>
+    <t>0.0066,0.7118,0.8811,0.0036</t>
+  </si>
+  <si>
+    <t>0.9898,0.0033,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.2676,0.8203,0.0033,0.0045</t>
+  </si>
+  <si>
+    <t>0.9905,0.0004,0.0000,0.0060</t>
+  </si>
+  <si>
+    <t>0.4799,0.6166,0.0044,0.0071</t>
+  </si>
+  <si>
+    <t>0.9880,0.0034,0.0022,0.0021</t>
+  </si>
+  <si>
+    <t>0.7893,0.0511,0.1357,0.0299</t>
+  </si>
+  <si>
+    <t>0.9833,0.0058,0.0024,0.0031</t>
+  </si>
+  <si>
+    <t>0.0000,0.0621,0.9834,0.0085</t>
+  </si>
+  <si>
+    <t>0.9542,0.0049,0.0025,0.0220</t>
+  </si>
+  <si>
+    <t>0.9442,0.0355,0.0142,0.0050</t>
+  </si>
+  <si>
+    <t>0.8685,0.1059,0.0291,0.0072</t>
+  </si>
+  <si>
+    <t>0.8469,0.1374,0.0172,0.0156</t>
+  </si>
+  <si>
+    <t>0.9575,0.0446,0.0035,0.0009</t>
+  </si>
+  <si>
+    <t>0.6754,0.1429,0.0038,0.1005</t>
+  </si>
+  <si>
+    <t>0.8084,0.2005,0.0331,0.0016</t>
+  </si>
+  <si>
+    <t>0.9076,0.0623,0.0048,0.0104</t>
+  </si>
+  <si>
+    <t>0.9909,0.0037,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.9890,0.0026,0.0001,0.0036</t>
+  </si>
+  <si>
+    <t>0.9958,0.0007,0.0000,0.0015</t>
+  </si>
+  <si>
+    <t>0.9854,0.0003,0.0007,0.0147</t>
+  </si>
+  <si>
+    <t>0.9673,0.0270,0.0058,0.0025</t>
+  </si>
+  <si>
+    <t>0.9925,0.0011,0.0001,0.0029</t>
+  </si>
+  <si>
+    <t>0.9917,0.0029,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9966,0.0004,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.4383,0.7065,0.0143,0.0017</t>
+  </si>
+  <si>
+    <t>0.6320,0.4798,0.0241,0.0007</t>
+  </si>
+  <si>
+    <t>0.5657,0.6067,0.0110,0.0008</t>
+  </si>
+  <si>
+    <t>0.8510,0.1229,0.0541,0.0096</t>
+  </si>
+  <si>
+    <t>0.9799,0.0136,0.0027,0.0011</t>
+  </si>
+  <si>
+    <t>0.9460,0.0535,0.0104,0.0011</t>
+  </si>
+  <si>
+    <t>0.9909,0.0096,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9729,0.0129,0.0015,0.0034</t>
+  </si>
+  <si>
+    <t>0.0019,0.0144,0.9953,0.0008</t>
+  </si>
+  <si>
+    <t>0.9812,0.0151,0.0028,0.0008</t>
+  </si>
+  <si>
+    <t>0.0012,0.0148,0.9921,0.0042</t>
+  </si>
+  <si>
+    <t>0.0106,0.0505,0.9758,0.0012</t>
+  </si>
+  <si>
+    <t>0.0466,0.0046,0.9715,0.0057</t>
+  </si>
+  <si>
+    <t>0.0055,0.2081,0.9562,0.0062</t>
+  </si>
+  <si>
+    <t>0.0335,0.0389,0.9314,0.0041</t>
+  </si>
+  <si>
+    <t>0.0050,0.0056,0.9890,0.0037</t>
+  </si>
+  <si>
+    <t>0.0140,0.0199,0.9717,0.0063</t>
+  </si>
+  <si>
+    <t>0.2671,0.0681,0.7653,0.0039</t>
+  </si>
+  <si>
+    <t>0.5815,0.0187,0.5375,0.0177</t>
+  </si>
+  <si>
+    <t>0.5455,0.0822,0.4751,0.0182</t>
+  </si>
+  <si>
+    <t>0.6399,0.0925,0.3300,0.0138</t>
+  </si>
+  <si>
+    <t>0.1664,0.2236,0.6640,0.0051</t>
+  </si>
+  <si>
+    <t>0.5554,0.0208,0.6200,0.0072</t>
+  </si>
+  <si>
+    <t>0.7424,0.0336,0.2518,0.0078</t>
+  </si>
+  <si>
+    <t>0.2321,0.4737,0.3483,0.0048</t>
+  </si>
+  <si>
+    <t>0.9451,0.0836,0.0039,0.0020</t>
+  </si>
+  <si>
+    <t>0.9774,0.0515,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9508,0.0577,0.0061,0.0018</t>
+  </si>
+  <si>
+    <t>0.9901,0.0124,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9348,0.1203,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.6461,0.0824,0.1728,0.0814</t>
+  </si>
+  <si>
+    <t>0.7418,0.0254,0.1851,0.0279</t>
+  </si>
+  <si>
+    <t>0.7967,0.0228,0.0965,0.0323</t>
+  </si>
+  <si>
+    <t>0.8171,0.0341,0.0956,0.0120</t>
+  </si>
+  <si>
+    <t>0.2364,0.0864,0.7198,0.0531</t>
+  </si>
+  <si>
+    <t>0.0096,0.0362,0.9315,0.1339</t>
+  </si>
+  <si>
+    <t>0.0143,0.0393,0.9291,0.0322</t>
+  </si>
+  <si>
+    <t>0.0097,0.0214,0.9710,0.0025</t>
+  </si>
+  <si>
+    <t>0.2272,0.0318,0.7676,0.0293</t>
+  </si>
+  <si>
+    <t>0.0190,0.1976,0.9016,0.0063</t>
+  </si>
+  <si>
+    <t>0.9844,0.0041,0.0003,0.0057</t>
+  </si>
+  <si>
+    <t>0.9883,0.0077,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9895,0.0034,0.0001,0.0025</t>
+  </si>
+  <si>
+    <t>0.9946,0.0027,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9916,0.0070,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9920,0.0092,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9969,0.0008,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9857,0.0099,0.0020,0.0011</t>
+  </si>
+  <si>
+    <t>0.0663,0.0056,0.9740,0.0037</t>
+  </si>
+  <si>
+    <t>0.4146,0.1847,0.5801,0.0041</t>
+  </si>
+  <si>
+    <t>0.6891,0.0167,0.1154,0.1192</t>
+  </si>
+  <si>
+    <t>0.0070,0.0036,0.9861,0.0085</t>
+  </si>
+  <si>
+    <t>0.0023,0.0267,0.9779,0.0170</t>
+  </si>
+  <si>
+    <t>0.0450,0.0601,0.8963,0.0149</t>
+  </si>
+  <si>
+    <t>0.0086,0.0062,0.9840,0.0059</t>
+  </si>
+  <si>
+    <t>0.0506,0.0167,0.9395,0.0057</t>
+  </si>
+  <si>
+    <t>0.0015,0.0083,0.9917,0.0075</t>
+  </si>
+  <si>
+    <t>0.0041,0.0153,0.9796,0.0178</t>
+  </si>
+  <si>
+    <t>0.0982,0.0379,0.9042,0.0074</t>
+  </si>
+  <si>
+    <t>0.4592,0.0135,0.4945,0.0655</t>
+  </si>
+  <si>
+    <t>0.6713,0.0080,0.4301,0.0175</t>
+  </si>
+  <si>
+    <t>0.8433,0.0104,0.0829,0.0155</t>
+  </si>
+  <si>
+    <t>0.9941,0.0053,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0009,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9927,0.0036,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9832,0.0332,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9953,0.0019,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9963,0.0013,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9922,0.0061,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9906,0.0050,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.0320,0.1561,0.8465,0.0029</t>
+  </si>
+  <si>
+    <t>0.0018,0.0497,0.9903,0.0015</t>
+  </si>
+  <si>
+    <t>0.0561,0.1143,0.8766,0.0105</t>
+  </si>
+  <si>
+    <t>0.0823,0.4556,0.5405,0.0073</t>
+  </si>
+  <si>
+    <t>0.0216,0.0220,0.9526,0.0192</t>
+  </si>
+  <si>
+    <t>0.1067,0.0341,0.1774,0.8216</t>
+  </si>
+  <si>
+    <t>0.1730,0.0110,0.8890,0.0058</t>
+  </si>
+  <si>
+    <t>0.0210,0.1042,0.9051,0.0191</t>
+  </si>
+  <si>
+    <t>0.2302,0.0005,0.0056,0.8951</t>
+  </si>
+  <si>
+    <t>0.0810,0.0210,0.0007,0.9550</t>
+  </si>
+  <si>
+    <t>0.0619,0.0023,0.0009,0.9806</t>
+  </si>
+  <si>
+    <t>0.0063,0.0006,0.0007,0.9970</t>
+  </si>
+  <si>
+    <t>0.0024,0.0002,0.0002,0.9989</t>
+  </si>
+  <si>
+    <t>0.7801,0.0686,0.0076,0.0723</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,10 +2175,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2413,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,10 +2497,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,10 +3505,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3869,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4611,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4642,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5412,7 @@
         <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,10 +5437,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
